--- a/business_forms/040_product_development_skills_assessment_form--business_forms.xlsx
+++ b/business_forms/040_product_development_skills_assessment_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'new_york'}</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'New York'}</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'los_angeles'}</t>
+          <t>los_angeles</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Los Angeles'}</t>
+          <t>Los Angeles</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'chicago'}</t>
+          <t>chicago</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Chicago'}</t>
+          <t>Chicago</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'project_management'}</t>
+          <t>project_management</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Project Management'}</t>
+          <t>Project Management</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'product_design'}</t>
+          <t>product_design</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Product Design'}</t>
+          <t>Product Design</t>
         </is>
       </c>
     </row>
@@ -1216,46 +1216,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'product_development'}</t>
+          <t>product_development</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Product Development'}</t>
+          <t>Product Development</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>skill_1_choices</t>
+          <t>skill_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'project_management'}</t>
+          <t>project_management</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Project Management'}</t>
+          <t>Project Management</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>skill_1_choices</t>
+          <t>skill_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'product_design'}</t>
+          <t>product_design</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Product Design'}</t>
+          <t>Product Design</t>
         </is>
       </c>
     </row>
@@ -1267,46 +1267,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'project_management'}</t>
+          <t>product_development</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Project Management'}</t>
+          <t>Product Development</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>skill_2_choices</t>
+          <t>skill_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'product_design'}</t>
+          <t>project_management</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Product Design'}</t>
+          <t>Project Management</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>skill_2_choices</t>
+          <t>skill_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'product_development'}</t>
+          <t>product_design</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Product Development'}</t>
+          <t>Product Design</t>
         </is>
       </c>
     </row>
@@ -1318,46 +1318,46 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'project_management'}</t>
+          <t>product_development</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Project Management'}</t>
+          <t>Product Development</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>skill_3_choices</t>
+          <t>skill_4_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'product_design'}</t>
+          <t>project_management</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Product Design'}</t>
+          <t>Project Management</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>skill_3_choices</t>
+          <t>skill_4_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'product_development'}</t>
+          <t>product_design</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Product Development'}</t>
+          <t>Product Design</t>
         </is>
       </c>
     </row>
@@ -1369,46 +1369,46 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'project_management'}</t>
+          <t>product_development</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Project Management'}</t>
+          <t>Product Development</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>skill_4_choices</t>
+          <t>skill_5_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'product_design'}</t>
+          <t>project_management</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Product Design'}</t>
+          <t>Project Management</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>skill_4_choices</t>
+          <t>skill_5_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'product_development'}</t>
+          <t>product_design</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Product Development'}</t>
+          <t>Product Design</t>
         </is>
       </c>
     </row>
@@ -1420,46 +1420,46 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'project_management'}</t>
+          <t>product_development</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Project Management'}</t>
+          <t>Product Development</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>skill_5_choices</t>
+          <t>skill_6_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'product_design'}</t>
+          <t>project_management</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Product Design'}</t>
+          <t>Project Management</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>skill_5_choices</t>
+          <t>skill_6_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'product_development'}</t>
+          <t>product_design</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Product Development'}</t>
+          <t>Product Design</t>
         </is>
       </c>
     </row>
@@ -1471,46 +1471,46 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'project_management'}</t>
+          <t>product_development</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Project Management'}</t>
+          <t>Product Development</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>skill_6_choices</t>
+          <t>product_type_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'product_design'}</t>
+          <t>software_product</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Product Design'}</t>
+          <t>Software Product</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>skill_6_choices</t>
+          <t>product_type_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'product_development'}</t>
+          <t>hardware_product</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Product Development'}</t>
+          <t>Hardware Product</t>
         </is>
       </c>
     </row>
@@ -1522,46 +1522,46 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'software_product'}</t>
+          <t>service_product</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Software Product'}</t>
+          <t>Service Product</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>product_type_choices</t>
+          <t>team_lead_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'hardware_product'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Hardware Product'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>product_type_choices</t>
+          <t>team_lead_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'service_product'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Service Product'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1573,46 +1573,46 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'john'}</t>
+          <t>joe</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'John'}</t>
+          <t>Joe</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>team_lead_choices</t>
+          <t>project_lead_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'jane'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Jane'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>team_lead_choices</t>
+          <t>project_lead_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'joe'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Joe'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1624,46 +1624,46 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'john'}</t>
+          <t>joe</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'John'}</t>
+          <t>Joe</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>project_lead_choices</t>
+          <t>skill_7_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'jane'}</t>
+          <t>project_management</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Jane'}</t>
+          <t>Project Management</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>project_lead_choices</t>
+          <t>skill_7_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'joe'}</t>
+          <t>product_design</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Joe'}</t>
+          <t>Product Design</t>
         </is>
       </c>
     </row>
@@ -1675,46 +1675,46 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'project_management'}</t>
+          <t>product_development</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Project Management'}</t>
+          <t>Product Development</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>skill_7_choices</t>
+          <t>skill_8_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'product_design'}</t>
+          <t>project_management</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Product Design'}</t>
+          <t>Project Management</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>skill_7_choices</t>
+          <t>skill_8_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'product_development'}</t>
+          <t>product_design</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Product Development'}</t>
+          <t>Product Design</t>
         </is>
       </c>
     </row>
@@ -1726,46 +1726,46 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'project_management'}</t>
+          <t>product_development</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Project Management'}</t>
+          <t>Product Development</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>skill_8_choices</t>
+          <t>skill_9_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'product_design'}</t>
+          <t>project_management</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Product Design'}</t>
+          <t>Project Management</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>skill_8_choices</t>
+          <t>skill_9_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'product_development'}</t>
+          <t>product_design</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Product Development'}</t>
+          <t>Product Design</t>
         </is>
       </c>
     </row>
@@ -1777,46 +1777,46 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'project_management'}</t>
+          <t>product_development</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Project Management'}</t>
+          <t>Product Development</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>skill_9_choices</t>
+          <t>project_status_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'product_design'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Product Design'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>skill_9_choices</t>
+          <t>project_status_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'product_development'}</t>
+          <t>on_hold</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Product Development'}</t>
+          <t>On Hold</t>
         </is>
       </c>
     </row>
@@ -1828,46 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'in_progress'}</t>
+          <t>done</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'In Progress'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>project_status_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'on_hold'}</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'On Hold'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>project_status_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'done'}</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'Done'}</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
